--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,620 +503,620 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Architect – Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>YT Global Network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7f6c18f0b40b42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
+          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect &amp; Reporting Solutions D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
+          <t>https://www.indeed.com/viewjob?jk=410011ba5535efbe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect &amp; Reporting Solutions D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccbbb87c6afe8cb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer-5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
+          <t>https://www.indeed.com/viewjob?jk=ecebbc9dd29cefa7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer-5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d1627d5b089666</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.1</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,172 +1126,172 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.8</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect &amp; Reporting Solutions D</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccbbb87c6afe8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Developer-5</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecebbc9dd29cefa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Developer-5</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d1627d5b089666</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,15 +2543,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b55676772b11e69</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b55676772b11e69</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer (Python ETL)</t>
+          <t>GCP AI Engineer - Cambridge, MA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Varteq</t>
+          <t>Lumeris</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, ETL, Docker, Airflow</t>
+          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805875ce39161cef</t>
+          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,15 +4336,50 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior GCP Data Architect – Remote</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YT Global Network</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7f6c18f0b40b42</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Senior GCP Data Architect – Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>YT Global Network</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7f6c18f0b40b42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Architect &amp; Reporting Solutions D</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410011ba5535efbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccbbb87c6afe8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=410011ba5535efbe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect &amp; Reporting Solutions D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccbbb87c6afe8cb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Developer-5</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecebbc9dd29cefa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d1627d5b089666</t>
+          <t>https://www.indeed.com/viewjob?jk=ecebbc9dd29cefa7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Java Developer-5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d1627d5b089666</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,69 +1816,69 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3302c4147ab0b0cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b55676772b11e69</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,129 +3716,129 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b55676772b11e69</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GCP AI Engineer - Cambridge, MA</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lumeris</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>GCP AI Engineer - Cambridge, MA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lumeris</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,15 +4371,190 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior System Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Datavault AI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=3302c4147ab0b0cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3302c4147ab0b0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>GCP AI Engineer - Cambridge, MA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Lumeris</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GCP AI Engineer - Cambridge, MA</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lumeris</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4520,41 +4520,6 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior GCP Data Architect – Remote</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YT Global Network</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7f6c18f0b40b42</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Architect &amp; Reporting Solutions D</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410011ba5535efbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Architect &amp; Reporting Solutions D</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccbbb87c6afe8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Developer-5</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecebbc9dd29cefa7</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Developer-5</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d1627d5b089666</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,116 +1217,116 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf22705d96e61e</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior System Architect</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Datavault AI</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755724cf9bc70aef</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3302c4147ab0b0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fc9f0307dc4aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,42 +3391,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,102 +3681,102 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b55676772b11e69</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,532 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Junior DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>GCP AI Engineer - Cambridge, MA</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Lumeris</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>EMR, IAM, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack - UI/UX Focus)- North America Software Center</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>TSMC</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Vancouver, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa81374f258fc366</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,60 +888,60 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,104 +2061,104 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9bbf23d77dfc12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,77 +3391,77 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,77 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5a21d896e67e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5a21d896e67e9f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -876,29 +876,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ScaleHealthTech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9bbf23d77dfc12</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,207 +3471,207 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2bea7326a4970d38</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2143304ae215ab</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sr Java Backend Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b81d52c01d7856d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,102 +3716,102 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b588911fd6c0bd0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,400 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6db760ee05781078</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Near-Miss Management</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=6856b750d699d0b8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Sr. .Net Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>SolutionStream</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Oracle, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c064b7d4a7d09b7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ScaleHealthTech</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,69 +2831,69 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,69 +3776,69 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b588911fd6c0bd0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b588911fd6c0bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db760ee05781078</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Near-Miss Management</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,87 +4371,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+          <t>https://www.indeed.com/viewjob?jk=6db760ee05781078</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6856b750d699d0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MassMutual</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=c4075abed317d9ce</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. .Net Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SolutionStream</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Oracle, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c064b7d4a7d09b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hive, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d10853c428fd34</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,49 +3086,49 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,73 +3142,73 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,182 +3461,182 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bea7326a4970d38</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2143304ae215ab</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Java Backend Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b81d52c01d7856d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6770f045e0af216</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,102 +3646,102 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,59 +3751,59 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b588911fd6c0bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Near-Miss Management</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,367 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6db760ee05781078</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=a8d1ad994188d3b1</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,77 +898,77 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,112 +1116,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MassMutual</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4075abed317d9ce</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,154 +1301,154 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4075abed317d9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,42 +1458,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d99c8b4bb53bb2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6464cc02853476</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,50 +2718,50 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ea949a8522ee45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Kafka Full stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,182 +2796,182 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b524889b9b023e4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,94 +3016,94 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=c7379b2166e4a5ff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,77 +3146,77 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,49 +3226,49 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,50 +3278,50 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Software Developer / Software Engineer (Dallas/Fort Worth - Hybrid)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EnergyBot</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,402 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Cassandra, Terraform, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5b4ec2f38d6dbf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8d1ad994188d3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,112 +1186,112 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4075abed317d9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,164 +1476,164 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d99c8b4bb53bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6464cc02853476</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,94 +2421,94 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,172 +2526,172 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,129 +2701,129 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ea949a8522ee45</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kafka Full stack Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b524889b9b023e4</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,59 +2831,59 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,15 +2893,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7379b2166e4a5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,402 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Developer / Software Engineer (Dallas/Fort Worth - Hybrid)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>EnergyBot</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Cassandra, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5b4ec2f38d6dbf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,104 +1081,104 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Senior SIEM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,77 +2306,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,190 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>AWS Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0c6d0c8aef2fbf</t>
         </is>
       </c>
     </row>
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior SIEM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior SIEM Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Atlanta (Remote Friendly)</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Vertex AI, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d237ba58e55ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,77 +1581,77 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,52 +2026,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,87 +2936,87 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Wenger Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Data and Systems Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clean Power Alliance</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=27cf2ef4404e94ae</t>
         </is>
       </c>
     </row>
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (CLAW)</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Developer (Remote Opportunity)</t>
+          <t>Senior Software Engineer (CLAW)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0c6d0c8aef2fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7b6f396b10f8f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>AWS Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0c6d0c8aef2fbf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2311,29 +2311,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
@@ -2428,52 +2428,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hudson Oaks, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Software Test Automation Framework Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=9219da3b5ceab951</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=ce538e24964a3f07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=979fbd96452ea4ce</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Wenger Group</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data and Systems Architect</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Clean Power Alliance</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27cf2ef4404e94ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Wenger Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data and Systems Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clean Power Alliance</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=27cf2ef4404e94ae</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
@@ -3437,6 +3437,76 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Developer (Remote Opportunity)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0c6d0c8aef2fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea5bb501a5ac8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SIEM Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intern, Software Engineer(Data Infrastructure)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Intern, Software Engineer(Data Infrastructure)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b61e16e9da8276</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Senior Backend Engineer - Startup(AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Taglynk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
@@ -2043,25 +2043,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vital Care Infusion Services, LLC</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Data Pipeline Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vital Care Infusion Services, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4125fc52d3ecd9f0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer II – AWS</t>
+          <t>Sr. Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCSS</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6071ff182d1660</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Test Automation Framework Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9219da3b5ceab951</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce538e24964a3f07</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fbd96452ea4ce</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,139 +2971,139 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Wenger Group</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data and Systems Architect</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Clean Power Alliance</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27cf2ef4404e94ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,147 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-01.xlsx
+++ b/results/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5a21d896e67e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
@@ -1098,52 +1098,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Field Engineer - Data Integration &amp; AI</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc90a9db157baf6</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6431593ad2d894f2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Senior Software Engineer (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Platform</t>
+          <t>Software Engineer - SQL (contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6071ff182d1660</t>
+          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a3d6523273721c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69201f5451e21bf3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,139 +2971,139 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Programmer Analyst (Enterprise Integration &amp; Content Services)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Oracle, SQL Server, ETL, Talend, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3da4fd635520fc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>AI Engineer II - Onsite, Springfield, MO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+          <t>https://www.indeed.com/viewjob?jk=cb93d64bc5d3b638</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>App Sys Analysis/Prgmming Mgr</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Scala, ETL, ELT, dbt, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=13dee544bdc70bb6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Administration &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,402 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ae59d4b6408a04b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b944869c6bc2e2ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5fc799481aebd64</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Searchpros Staffing</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43afc506f9234f19</t>
         </is>
       </c>
     </row>
